--- a/samples/corpus/full/entreprise/margin-dashboard/2026-04-10_tableau-de-bord-des-marges.xlsx
+++ b/samples/corpus/full/entreprise/margin-dashboard/2026-04-10_tableau-de-bord-des-marges.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Marge à date HT</t>
+          <t>Écart facturé / déboursé HT</t>
         </is>
       </c>
     </row>
